--- a/AAII_Financials/Yearly/UPS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UPS_YR_FIN.xlsx
@@ -1010,7 +1010,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>834000</v>
+        <v>892000</v>
       </c>
       <c r="E14" s="3">
         <v>368000</v>
@@ -1061,7 +1061,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>3746000</v>
+        <v>3688000</v>
       </c>
       <c r="E15" s="3">
         <v>3609000</v>
@@ -1130,7 +1130,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>80137000</v>
+        <v>80079000</v>
       </c>
       <c r="E17" s="3">
         <v>83059000</v>
@@ -1181,7 +1181,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>8524000</v>
+        <v>8582000</v>
       </c>
       <c r="E18" s="3">
         <v>8011000</v>
